--- a/verification/cases/roundtrip/formulas_math_trig/init.xlsx
+++ b/verification/cases/roundtrip/formulas_math_trig/init.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10110"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/frl/Desktop/shortcut/stash/excel-test-sets/data/math-trig/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\frl\AppData\Local\Temp\xlsx-export-inits-3946636136\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89145CA2-5769-0040-9B7C-494F282A18B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F10D9269-D313-4967-B499-EB0B621B1420}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1260" yWindow="660" windowWidth="28680" windowHeight="17480" xr2:uid="{2B82E61A-D437-2145-9148-17D3499E77D3}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{2B82E61A-D437-2145-9148-17D3499E77D3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -731,7 +731,7 @@
 
 <file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
 <wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
-  <wetp:taskpane dockstate="right" visibility="0" width="350" row="0">
+  <wetp:taskpane dockstate="right" visibility="1" width="438" row="0">
     <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </wetp:taskpane>
 </wetp:taskpanes>
@@ -754,19 +754,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AAF37C9D-1CA2-1649-A1DA-C609654B06B8}">
   <dimension ref="B2:K162"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="50" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="60.1640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="9.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="60.19921875" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="9.19921875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.1640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.1640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.19921875" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="8.69921875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:11" ht="19" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:11" ht="18" x14ac:dyDescent="0.35">
       <c r="B2" s="1" t="s">
         <v>4</v>
       </c>
@@ -780,7 +780,7 @@
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
     </row>
-    <row r="4" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B4" s="5" t="s">
         <v>5</v>
       </c>
@@ -794,7 +794,7 @@
       <c r="J4" s="5"/>
       <c r="K4" s="5"/>
     </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B5" s="3" t="s">
         <v>0</v>
       </c>
@@ -810,7 +810,7 @@
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
     </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B6" s="3" t="s">
         <v>6</v>
       </c>
@@ -827,7 +827,7 @@
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
     </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B7" s="3" t="s">
         <v>7</v>
       </c>
@@ -844,7 +844,7 @@
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
     </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B8" s="3" t="s">
         <v>8</v>
       </c>
@@ -861,7 +861,7 @@
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
     </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B9" s="3" t="s">
         <v>9</v>
       </c>
@@ -878,7 +878,7 @@
       <c r="J9" s="2"/>
       <c r="K9" s="2"/>
     </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B10" s="3" t="s">
         <v>10</v>
       </c>
@@ -895,7 +895,7 @@
       <c r="J10" s="2"/>
       <c r="K10" s="2"/>
     </row>
-    <row r="11" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B11" s="3" t="s">
         <v>11</v>
       </c>
@@ -912,7 +912,7 @@
       <c r="J11" s="2"/>
       <c r="K11" s="2"/>
     </row>
-    <row r="12" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B12" s="3" t="s">
         <v>12</v>
       </c>
@@ -929,7 +929,7 @@
       <c r="J12" s="2"/>
       <c r="K12" s="2"/>
     </row>
-    <row r="13" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B13" s="3" t="s">
         <v>13</v>
       </c>
@@ -946,7 +946,7 @@
       <c r="J13" s="2"/>
       <c r="K13" s="2"/>
     </row>
-    <row r="14" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:11" x14ac:dyDescent="0.3">
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
       <c r="F14" s="2"/>
@@ -956,7 +956,7 @@
       <c r="J14" s="2"/>
       <c r="K14" s="2"/>
     </row>
-    <row r="15" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:11" x14ac:dyDescent="0.3">
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
@@ -966,7 +966,7 @@
       <c r="J15" s="2"/>
       <c r="K15" s="2"/>
     </row>
-    <row r="16" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B16" s="9" t="s">
         <v>14</v>
       </c>
@@ -980,7 +980,7 @@
       <c r="J16" s="5"/>
       <c r="K16" s="5"/>
     </row>
-    <row r="17" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B17" s="11" t="s">
         <v>1</v>
       </c>
@@ -1003,7 +1003,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="18" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B18" s="6" t="str">
         <f>$B$5</f>
         <v>Zero</v>
@@ -1033,7 +1033,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="19" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B19" s="6" t="str">
         <f>$B$6</f>
         <v>π/6 (30°)</v>
@@ -1063,7 +1063,7 @@
         <v>1.7320508075688776</v>
       </c>
     </row>
-    <row r="20" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B20" s="6" t="str">
         <f>$B$7</f>
         <v>π/4 (45°)</v>
@@ -1093,7 +1093,7 @@
         <v>1.0000000000000002</v>
       </c>
     </row>
-    <row r="21" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B21" s="6" t="str">
         <f>$B$8</f>
         <v>π/3 (60°)</v>
@@ -1123,7 +1123,7 @@
         <v>0.57735026918962595</v>
       </c>
     </row>
-    <row r="22" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B22" s="6" t="str">
         <f>$B$9</f>
         <v>π/2 (90°)</v>
@@ -1153,7 +1153,7 @@
         <v>6.123233995736766E-17</v>
       </c>
     </row>
-    <row r="23" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B23" s="6" t="str">
         <f>$B$10</f>
         <v>π (180°)</v>
@@ -1183,7 +1183,7 @@
         <v>-8165619676597685</v>
       </c>
     </row>
-    <row r="24" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B24" s="6" t="str">
         <f>$B$11</f>
         <v>3π/2 (270°)</v>
@@ -1213,7 +1213,7 @@
         <v>1.8369701987210299E-16</v>
       </c>
     </row>
-    <row r="25" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B25" s="6" t="str">
         <f>$B$12</f>
         <v>2π (360°)</v>
@@ -1243,7 +1243,7 @@
         <v>-4082809838298842.5</v>
       </c>
     </row>
-    <row r="26" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B26" s="6" t="str">
         <f>$B$13</f>
         <v>-π/4 (-45°)</v>
@@ -1273,7 +1273,7 @@
         <v>-1.0000000000000002</v>
       </c>
     </row>
-    <row r="28" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B28" s="5" t="s">
         <v>21</v>
       </c>
@@ -1287,7 +1287,7 @@
       <c r="J28" s="5"/>
       <c r="K28" s="5"/>
     </row>
-    <row r="30" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B30" s="5" t="s">
         <v>22</v>
       </c>
@@ -1301,7 +1301,7 @@
       <c r="J30" s="5"/>
       <c r="K30" s="5"/>
     </row>
-    <row r="31" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B31" s="3">
         <v>-1</v>
       </c>
@@ -1309,7 +1309,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="32" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B32" s="3" t="s">
         <v>23</v>
       </c>
@@ -1318,7 +1318,7 @@
         <v>-0.8660254037844386</v>
       </c>
     </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B33" s="3" t="s">
         <v>24</v>
       </c>
@@ -1327,7 +1327,7 @@
         <v>-0.70710678118654757</v>
       </c>
     </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B34" s="3">
         <v>-0.5</v>
       </c>
@@ -1335,7 +1335,7 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B35" s="3">
         <v>0</v>
       </c>
@@ -1343,7 +1343,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B36" s="3">
         <v>0.5</v>
       </c>
@@ -1351,7 +1351,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B37" s="3" t="s">
         <v>25</v>
       </c>
@@ -1360,7 +1360,7 @@
         <v>0.70710678118654757</v>
       </c>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B38" s="3" t="s">
         <v>26</v>
       </c>
@@ -1369,7 +1369,7 @@
         <v>0.8660254037844386</v>
       </c>
     </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B39" s="3">
         <v>1</v>
       </c>
@@ -1377,7 +1377,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B41" s="5" t="s">
         <v>27</v>
       </c>
@@ -1391,7 +1391,7 @@
       <c r="J41" s="5"/>
       <c r="K41" s="5"/>
     </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B42" s="11" t="s">
         <v>1</v>
       </c>
@@ -1405,7 +1405,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B43" s="6">
         <f>$B$31</f>
         <v>-1</v>
@@ -1423,7 +1423,7 @@
         <v>-0.78539816339744828</v>
       </c>
     </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B44" s="6" t="str">
         <f>$B$32</f>
         <v>-√3/2</v>
@@ -1441,7 +1441,7 @@
         <v>-0.71372437894476559</v>
       </c>
     </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B45" s="6" t="str">
         <f>$B$33</f>
         <v>-√2/2</v>
@@ -1459,7 +1459,7 @@
         <v>-0.61547970867038737</v>
       </c>
     </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B46" s="6">
         <f>$B$34</f>
         <v>-0.5</v>
@@ -1477,7 +1477,7 @@
         <v>-0.46364760900080615</v>
       </c>
     </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B47" s="6">
         <f>$B$35</f>
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B48" s="6">
         <f>$B$36</f>
         <v>0.5</v>
@@ -1513,7 +1513,7 @@
         <v>0.46364760900080615</v>
       </c>
     </row>
-    <row r="49" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="49" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B49" s="6" t="str">
         <f>$B$37</f>
         <v>√2/2</v>
@@ -1531,7 +1531,7 @@
         <v>0.61547970867038737</v>
       </c>
     </row>
-    <row r="50" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="50" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B50" s="6" t="str">
         <f>$B$38</f>
         <v>√3/2</v>
@@ -1549,7 +1549,7 @@
         <v>0.71372437894476559</v>
       </c>
     </row>
-    <row r="51" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="51" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B51" s="6">
         <f>$B$39</f>
         <v>1</v>
@@ -1567,7 +1567,7 @@
         <v>0.78539816339744828</v>
       </c>
     </row>
-    <row r="53" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="53" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B53" s="5" t="s">
         <v>31</v>
       </c>
@@ -1581,7 +1581,7 @@
       <c r="J53" s="5"/>
       <c r="K53" s="5"/>
     </row>
-    <row r="54" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="54" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B54" s="11" t="s">
         <v>1</v>
       </c>
@@ -1595,7 +1595,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="55" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="55" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B55" s="6" t="str">
         <f>$B$5</f>
         <v>Zero</v>
@@ -1613,7 +1613,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="56" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B56" s="6" t="str">
         <f>$B$6</f>
         <v>π/6 (30°)</v>
@@ -1631,7 +1631,7 @@
         <v>0.48234790710102493</v>
       </c>
     </row>
-    <row r="57" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="57" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B57" s="6" t="str">
         <f>$B$7</f>
         <v>π/4 (45°)</v>
@@ -1649,7 +1649,7 @@
         <v>0.66577375002835382</v>
       </c>
     </row>
-    <row r="58" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="58" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B58" s="6" t="str">
         <f>$B$8</f>
         <v>π/3 (60°)</v>
@@ -1667,7 +1667,7 @@
         <v>0.80844879263002201</v>
       </c>
     </row>
-    <row r="59" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="59" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B59" s="6" t="str">
         <f>$B$9</f>
         <v>π/2 (90°)</v>
@@ -1685,7 +1685,7 @@
         <v>1.0038848218538872</v>
       </c>
     </row>
-    <row r="60" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="60" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B60" s="6" t="str">
         <f>$B$10</f>
         <v>π (180°)</v>
@@ -1703,7 +1703,7 @@
         <v>1.2626272556789115</v>
       </c>
     </row>
-    <row r="61" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="61" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B61" s="6" t="str">
         <f>$B$11</f>
         <v>3π/2 (270°)</v>
@@ -1721,7 +1721,7 @@
         <v>1.3616916829711636</v>
       </c>
     </row>
-    <row r="62" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="62" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B62" s="6" t="str">
         <f>$B$12</f>
         <v>2π (360°)</v>
@@ -1739,7 +1739,7 @@
         <v>1.4129651365067377</v>
       </c>
     </row>
-    <row r="63" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="63" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B63" s="6" t="str">
         <f>$B$13</f>
         <v>-π/4 (-45°)</v>
@@ -1757,7 +1757,7 @@
         <v>-0.66577375002835382</v>
       </c>
     </row>
-    <row r="65" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B65" s="5" t="s">
         <v>32</v>
       </c>
@@ -1771,7 +1771,7 @@
       <c r="J65" s="5"/>
       <c r="K65" s="5"/>
     </row>
-    <row r="66" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B66" s="11" t="s">
         <v>33</v>
       </c>
@@ -1812,7 +1812,7 @@
         <v>-0.78539816339744828</v>
       </c>
     </row>
-    <row r="67" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B67" s="8">
         <f>$C$5</f>
         <v>0</v>
@@ -1854,7 +1854,7 @@
         <v>3.1415926535897931</v>
       </c>
     </row>
-    <row r="68" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B68" s="8">
         <f>$C$6</f>
         <v>0.52359877559829882</v>
@@ -1896,7 +1896,7 @@
         <v>2.5535900500422257</v>
       </c>
     </row>
-    <row r="69" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B69" s="8">
         <f>$C$7</f>
         <v>0.78539816339744828</v>
@@ -1938,7 +1938,7 @@
         <v>2.3561944901923448</v>
       </c>
     </row>
-    <row r="70" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B70" s="8">
         <f>$C$8</f>
         <v>1.0471975511965976</v>
@@ -1980,7 +1980,7 @@
         <v>2.2142974355881808</v>
       </c>
     </row>
-    <row r="71" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B71" s="8">
         <f>$C$9</f>
         <v>1.5707963267948966</v>
@@ -2022,7 +2022,7 @@
         <v>2.0344439357957027</v>
       </c>
     </row>
-    <row r="72" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B72" s="8">
         <f>$C$10</f>
         <v>3.1415926535897931</v>
@@ -2064,7 +2064,7 @@
         <v>1.8157749899217606</v>
       </c>
     </row>
-    <row r="73" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B73" s="8">
         <f>$C$11</f>
         <v>4.7123889803846897</v>
@@ -2106,7 +2106,7 @@
         <v>1.7359450042095232</v>
       </c>
     </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B74" s="8">
         <f>$C$12</f>
         <v>6.2831853071795862</v>
@@ -2148,7 +2148,7 @@
         <v>1.695151321341658</v>
       </c>
     </row>
-    <row r="75" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B75" s="8">
         <f>$C$13</f>
         <v>-0.78539816339744828</v>
@@ -2190,7 +2190,7 @@
         <v>-2.3561944901923448</v>
       </c>
     </row>
-    <row r="77" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B77" s="5" t="s">
         <v>34</v>
       </c>
@@ -2204,7 +2204,7 @@
       <c r="J77" s="5"/>
       <c r="K77" s="5"/>
     </row>
-    <row r="78" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="78" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B78" s="11" t="s">
         <v>1</v>
       </c>
@@ -2224,7 +2224,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="79" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B79" s="6" t="str">
         <f>$B$5</f>
         <v>Zero</v>
@@ -2250,7 +2250,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="80" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B80" s="6" t="str">
         <f>$B$6</f>
         <v>π/6 (30°)</v>
@@ -2276,7 +2276,7 @@
         <v>1.8253055746879534</v>
       </c>
     </row>
-    <row r="81" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="81" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B81" s="6" t="str">
         <f>$B$7</f>
         <v>π/4 (45°)</v>
@@ -2302,7 +2302,7 @@
         <v>1.1511838709208486</v>
       </c>
     </row>
-    <row r="82" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="82" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B82" s="6" t="str">
         <f>$B$8</f>
         <v>π/3 (60°)</v>
@@ -2328,7 +2328,7 @@
         <v>0.80040529288859308</v>
       </c>
     </row>
-    <row r="83" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="83" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B83" s="6" t="str">
         <f>$B$9</f>
         <v>π/2 (90°)</v>
@@ -2354,7 +2354,7 @@
         <v>0.43453720809469581</v>
       </c>
     </row>
-    <row r="84" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="84" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B84" s="6" t="str">
         <f>$B$10</f>
         <v>π (180°)</v>
@@ -2380,7 +2380,7 @@
         <v>8.6589537530046945E-2</v>
       </c>
     </row>
-    <row r="85" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="85" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B85" s="6" t="str">
         <f>$B$11</f>
         <v>3π/2 (270°)</v>
@@ -2406,7 +2406,7 @@
         <v>1.7968032053777287E-2</v>
       </c>
     </row>
-    <row r="86" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="86" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B86" s="6" t="str">
         <f>$B$12</f>
         <v>2π (360°)</v>
@@ -2432,7 +2432,7 @@
         <v>3.7348984882856731E-3</v>
       </c>
     </row>
-    <row r="87" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="87" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B87" s="6" t="str">
         <f>$B$13</f>
         <v>-π/4 (-45°)</v>
@@ -2458,7 +2458,7 @@
         <v>-1.1511838709208486</v>
       </c>
     </row>
-    <row r="89" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="89" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B89" s="5" t="s">
         <v>40</v>
       </c>
@@ -2472,7 +2472,7 @@
       <c r="J89" s="5"/>
       <c r="K89" s="5"/>
     </row>
-    <row r="90" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="90" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B90" s="5" t="s">
         <v>41</v>
       </c>
@@ -2486,7 +2486,7 @@
       <c r="J90" s="5"/>
       <c r="K90" s="5"/>
     </row>
-    <row r="91" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="91" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B91" s="3">
         <v>-10</v>
       </c>
@@ -2494,7 +2494,7 @@
         <v>-10</v>
       </c>
     </row>
-    <row r="92" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="92" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B92" s="3">
         <v>-1</v>
       </c>
@@ -2502,7 +2502,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="93" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="93" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B93" s="3">
         <v>-0.5</v>
       </c>
@@ -2510,7 +2510,7 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="94" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="94" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B94" s="3">
         <v>0</v>
       </c>
@@ -2518,7 +2518,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="95" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B95" s="3">
         <v>0.5</v>
       </c>
@@ -2526,7 +2526,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="96" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="96" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B96" s="3">
         <v>1</v>
       </c>
@@ -2534,7 +2534,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="97" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B97" s="3">
         <v>2</v>
       </c>
@@ -2542,7 +2542,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="98" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="98" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B98" s="3">
         <v>10</v>
       </c>
@@ -2550,7 +2550,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="99" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="99" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B99" s="3">
         <v>100</v>
       </c>
@@ -2558,7 +2558,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="101" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="101" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B101" s="5" t="s">
         <v>42</v>
       </c>
@@ -2572,7 +2572,7 @@
       <c r="J101" s="5"/>
       <c r="K101" s="5"/>
     </row>
-    <row r="102" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="102" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B102" s="11" t="s">
         <v>1</v>
       </c>
@@ -2586,7 +2586,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="103" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="103" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B103" s="6">
         <f>$B$91</f>
         <v>-10</v>
@@ -2604,7 +2604,7 @@
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="104" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="104" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B104" s="6">
         <f>$B$92</f>
         <v>-1</v>
@@ -2622,7 +2622,7 @@
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="105" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="105" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B105" s="6">
         <f>$B$93</f>
         <v>-0.5</v>
@@ -2640,7 +2640,7 @@
         <v>-0.54930614433405489</v>
       </c>
     </row>
-    <row r="106" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="106" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B106" s="6">
         <f>$B$94</f>
         <v>0</v>
@@ -2658,7 +2658,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="107" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B107" s="6">
         <f>$B$95</f>
         <v>0.5</v>
@@ -2676,7 +2676,7 @@
         <v>0.54930614433405489</v>
       </c>
     </row>
-    <row r="108" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="108" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B108" s="6">
         <f>$B$96</f>
         <v>1</v>
@@ -2694,7 +2694,7 @@
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="109" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="109" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B109" s="6">
         <f>$B$97</f>
         <v>2</v>
@@ -2712,7 +2712,7 @@
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="110" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="110" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B110" s="6">
         <f>$B$98</f>
         <v>10</v>
@@ -2730,7 +2730,7 @@
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="111" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="111" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B111" s="6">
         <f>$B$99</f>
         <v>100</v>
@@ -2748,7 +2748,7 @@
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="113" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="113" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B113" s="5" t="s">
         <v>46</v>
       </c>
@@ -2762,7 +2762,7 @@
       <c r="J113" s="5"/>
       <c r="K113" s="5"/>
     </row>
-    <row r="114" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="114" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B114" s="11" t="s">
         <v>1</v>
       </c>
@@ -2776,7 +2776,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="115" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="115" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B115" s="6" t="str">
         <f>$B$5</f>
         <v>Zero</v>
@@ -2794,7 +2794,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="116" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B116" s="6" t="str">
         <f>$B$6</f>
         <v>π/6 (30°)</v>
@@ -2812,7 +2812,7 @@
         <v>0.58128501169472302</v>
       </c>
     </row>
-    <row r="117" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="117" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B117" s="6" t="str">
         <f>$B$7</f>
         <v>π/4 (45°)</v>
@@ -2830,7 +2830,7 @@
         <v>1.059306170823243</v>
       </c>
     </row>
-    <row r="118" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="118" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B118" s="6" t="str">
         <f>$B$8</f>
         <v>π/3 (60°)</v>
@@ -2848,7 +2848,7 @@
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="119" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="119" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B119" s="6" t="str">
         <f>$B$9</f>
         <v>π/2 (90°)</v>
@@ -2866,7 +2866,7 @@
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="120" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="120" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B120" s="6" t="str">
         <f>$B$10</f>
         <v>π (180°)</v>
@@ -2884,7 +2884,7 @@
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="121" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="121" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B121" s="6" t="str">
         <f>$B$11</f>
         <v>3π/2 (270°)</v>
@@ -2902,7 +2902,7 @@
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="122" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="122" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B122" s="6" t="str">
         <f>$B$12</f>
         <v>2π (360°)</v>
@@ -2920,7 +2920,7 @@
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="123" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="123" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B123" s="6" t="str">
         <f>$B$13</f>
         <v>-π/4 (-45°)</v>
@@ -2938,7 +2938,7 @@
         <v>-1.0593061708232432</v>
       </c>
     </row>
-    <row r="125" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="125" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B125" s="5" t="s">
         <v>47</v>
       </c>
@@ -2952,7 +2952,7 @@
       <c r="J125" s="5"/>
       <c r="K125" s="5"/>
     </row>
-    <row r="126" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="126" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B126" s="5" t="s">
         <v>48</v>
       </c>
@@ -2966,7 +2966,7 @@
       <c r="J126" s="5"/>
       <c r="K126" s="5"/>
     </row>
-    <row r="127" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="127" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B127" s="11" t="s">
         <v>1</v>
       </c>
@@ -2977,7 +2977,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="128" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="128" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B128" s="6" t="s">
         <v>51</v>
       </c>
@@ -2990,7 +2990,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="129" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B129" s="6" t="s">
         <v>52</v>
       </c>
@@ -3003,7 +3003,7 @@
         <v>1718.8733853924696</v>
       </c>
     </row>
-    <row r="130" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="130" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B130" s="6" t="s">
         <v>53</v>
       </c>
@@ -3016,7 +3016,7 @@
         <v>2578.3100780887044</v>
       </c>
     </row>
-    <row r="131" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="131" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B131" s="6" t="s">
         <v>54</v>
       </c>
@@ -3029,7 +3029,7 @@
         <v>3437.7467707849391</v>
       </c>
     </row>
-    <row r="132" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="132" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B132" s="6" t="s">
         <v>55</v>
       </c>
@@ -3042,7 +3042,7 @@
         <v>5156.6201561774087</v>
       </c>
     </row>
-    <row r="133" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="133" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B133" s="6" t="s">
         <v>56</v>
       </c>
@@ -3055,7 +3055,7 @@
         <v>10313.240312354817</v>
       </c>
     </row>
-    <row r="134" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="134" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B134" s="6" t="s">
         <v>57</v>
       </c>
@@ -3068,7 +3068,7 @@
         <v>15469.860468532228</v>
       </c>
     </row>
-    <row r="135" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="135" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B135" s="6" t="s">
         <v>58</v>
       </c>
@@ -3081,7 +3081,7 @@
         <v>20626.480624709635</v>
       </c>
     </row>
-    <row r="136" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="136" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B136" s="6" t="s">
         <v>59</v>
       </c>
@@ -3094,7 +3094,7 @@
         <v>-2578.3100780887044</v>
       </c>
     </row>
-    <row r="138" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="138" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B138" s="9" t="s">
         <v>60</v>
       </c>
@@ -3108,7 +3108,7 @@
       <c r="J138" s="5"/>
       <c r="K138" s="5"/>
     </row>
-    <row r="139" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="139" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B139" s="11" t="s">
         <v>1</v>
       </c>
@@ -3119,7 +3119,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="140" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="140" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B140" s="6" t="str">
         <f>$B$5</f>
         <v>Zero</v>
@@ -3133,7 +3133,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="141" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B141" s="6" t="str">
         <f>$B$6</f>
         <v>π/6 (30°)</v>
@@ -3147,7 +3147,7 @@
         <v>29.999999999999996</v>
       </c>
     </row>
-    <row r="142" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="142" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B142" s="6" t="str">
         <f>$B$7</f>
         <v>π/4 (45°)</v>
@@ -3161,7 +3161,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="143" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="143" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B143" s="6" t="str">
         <f>$B$8</f>
         <v>π/3 (60°)</v>
@@ -3175,7 +3175,7 @@
         <v>59.999999999999993</v>
       </c>
     </row>
-    <row r="144" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="144" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B144" s="6" t="str">
         <f>$B$9</f>
         <v>π/2 (90°)</v>
@@ -3189,7 +3189,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="145" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="145" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B145" s="6" t="str">
         <f>$B$10</f>
         <v>π (180°)</v>
@@ -3203,7 +3203,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="146" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="146" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B146" s="6" t="str">
         <f>$B$11</f>
         <v>3π/2 (270°)</v>
@@ -3217,7 +3217,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="147" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="147" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B147" s="6" t="str">
         <f>$B$12</f>
         <v>2π (360°)</v>
@@ -3231,7 +3231,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="148" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="148" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B148" s="6" t="str">
         <f>$B$13</f>
         <v>-π/4 (-45°)</v>
@@ -3245,7 +3245,7 @@
         <v>-45</v>
       </c>
     </row>
-    <row r="150" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="150" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B150" s="5" t="s">
         <v>61</v>
       </c>
@@ -3259,7 +3259,7 @@
       <c r="J150" s="5"/>
       <c r="K150" s="5"/>
     </row>
-    <row r="151" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="151" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B151" s="6" t="s">
         <v>62</v>
       </c>
@@ -3268,7 +3268,7 @@
         <v>3.1415926535897931</v>
       </c>
     </row>
-    <row r="154" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="154" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B154" s="5" t="s">
         <v>2</v>
       </c>
@@ -3282,7 +3282,7 @@
       <c r="J154" s="5"/>
       <c r="K154" s="5"/>
     </row>
-    <row r="155" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="155" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B155" s="14" t="e">
         <v>#DIV/0!</v>
       </c>
@@ -3290,7 +3290,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="156" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="156" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B156" s="14" t="e">
         <v>#NUM!</v>
       </c>
@@ -3298,7 +3298,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="157" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="157" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B157" s="14" t="s">
         <v>3</v>
       </c>
@@ -3306,7 +3306,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="158" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="158" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B158" s="14" t="s">
         <v>66</v>
       </c>
@@ -3314,7 +3314,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="159" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="159" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B159" s="14" t="s">
         <v>68</v>
       </c>
@@ -3322,7 +3322,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="160" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="160" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B160" s="14" t="s">
         <v>70</v>
       </c>
@@ -3330,7 +3330,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="161" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="161" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B161" s="14" t="s">
         <v>72</v>
       </c>
@@ -3338,7 +3338,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="162" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="162" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B162" s="14" t="s">
         <v>74</v>
       </c>
